--- a/RS_D620/documents/ra6t2 pin.xlsx
+++ b/RS_D620/documents/ra6t2 pin.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://renesasgroup-my.sharepoint.com/personal/takuya_katayama_px_renesas_com/Documents/Documents/Products/D620/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repo\POC\RS_D620\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="461" documentId="8_{B77191B6-4090-49FA-B0B6-2846E68FF57E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E2B24DB-4308-4A7F-9FC2-44F21D9B9945}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BBD1D2C-3805-4D29-88C7-DD3097CFB8BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="420" yWindow="1155" windowWidth="21600" windowHeight="15180" activeTab="2" xr2:uid="{796A6475-E8F1-4464-8E38-7F0969700445}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{796A6475-E8F1-4464-8E38-7F0969700445}"/>
   </bookViews>
   <sheets>
     <sheet name="100 Base" sheetId="2" r:id="rId1"/>
@@ -152,7 +152,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="190">
   <si>
     <t>PA12</t>
   </si>
@@ -719,13 +719,16 @@
   </si>
   <si>
     <t>PE12</t>
+  </si>
+  <si>
+    <t>PD04 (85) and PD05 (86) do not appear to be JTAG.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -761,8 +764,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FFFFFF00"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -817,6 +827,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -830,7 +846,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -943,7 +959,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3463,16 +3483,18 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{518C23B1-C437-49C5-AAC0-A4AC9727D982}">
-  <dimension ref="A1:AC39"/>
+  <dimension ref="A1:AE39"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.28515625" style="6" bestFit="1" customWidth="1"/>
     <col min="2" max="28" width="3.28515625" style="1" customWidth="1"/>
     <col min="29" max="29" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="30" max="30" width="9.140625" style="1"/>
+    <col min="31" max="31" width="81.85546875" style="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="96.75" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:31" ht="96.75" x14ac:dyDescent="0.2">
       <c r="A1" s="29"/>
       <c r="B1" s="31"/>
       <c r="C1" s="10" t="s">
@@ -3553,7 +3575,7 @@
       <c r="AB1" s="31"/>
       <c r="AC1" s="31"/>
     </row>
-    <row r="2" spans="1:29" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:31" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="29"/>
       <c r="B2" s="31"/>
       <c r="C2" s="31">
@@ -3633,8 +3655,11 @@
       </c>
       <c r="AB2" s="31"/>
       <c r="AC2" s="31"/>
-    </row>
-    <row r="3" spans="1:29" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE2" s="45" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="28" t="s">
         <v>110</v>
       </c>
@@ -3673,7 +3698,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:31" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="28" t="s">
         <v>128</v>
       </c>
@@ -3712,7 +3737,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="5" spans="1:29" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="25" t="s">
         <v>119</v>
       </c>
@@ -3751,7 +3776,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="25" t="s">
         <v>120</v>
       </c>
@@ -3790,7 +3815,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="7" spans="1:29" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="25" t="s">
         <v>121</v>
       </c>
@@ -3825,11 +3850,11 @@
       <c r="AB7" s="31">
         <v>46</v>
       </c>
-      <c r="AC7" s="44" t="s">
+      <c r="AC7" s="46" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="8" spans="1:29" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="25" t="s">
         <v>122</v>
       </c>
@@ -3864,11 +3889,11 @@
       <c r="AB8" s="31">
         <v>45</v>
       </c>
-      <c r="AC8" s="44" t="s">
+      <c r="AC8" s="46" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="25" t="s">
         <v>123</v>
       </c>
@@ -3903,11 +3928,11 @@
       <c r="AB9" s="31">
         <v>44</v>
       </c>
-      <c r="AC9" s="44" t="s">
+      <c r="AC9" s="46" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="10" spans="1:29" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:31" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="25" t="s">
         <v>124</v>
       </c>
@@ -3941,11 +3966,11 @@
       <c r="AB10" s="31">
         <v>43</v>
       </c>
-      <c r="AC10" s="44" t="s">
+      <c r="AC10" s="46" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="11" spans="1:29" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:31" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="25" t="s">
         <v>125</v>
       </c>
@@ -3984,11 +4009,11 @@
         <v>55</v>
       </c>
     </row>
-    <row r="12" spans="1:29" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:31" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="28" t="s">
         <v>131</v>
       </c>
-      <c r="B12" s="31">
+      <c r="B12" s="44">
         <v>85</v>
       </c>
       <c r="C12" s="31"/>
@@ -4021,11 +4046,11 @@
         <v>56</v>
       </c>
     </row>
-    <row r="13" spans="1:29" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:31" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="28" t="s">
         <v>132</v>
       </c>
-      <c r="B13" s="31">
+      <c r="B13" s="44">
         <v>86</v>
       </c>
       <c r="C13" s="31"/>
@@ -4060,7 +4085,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:29" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:31" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
         <v>127</v>
       </c>
@@ -4100,7 +4125,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:29" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:31" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
         <v>15</v>
       </c>
@@ -4139,7 +4164,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="16" spans="1:29" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:31" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="28" t="s">
         <v>129</v>
       </c>
